--- a/output/看屋檢查清單_新北建案_2026-09-11_六_財務評估.xlsx
+++ b/output/看屋檢查清單_新北建案_2026-09-11_六_財務評估.xlsx
@@ -418,40 +418,40 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>以總價1,088萬計：貸80成870萬，月付約3.34萬（2.29%）／約3.12萬（新青安1.775%）</t>
+          <t>以總價1,088萬計：貸8成870萬，月付約3.34萬（2.29%）／約3.12萬（新青安1.775%）</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>以總價999萬計：貸80成799萬，月付約3.07萬（2.29%）／約2.86萬（新青安1.775%）</t>
+          <t>以總價999萬計：貸8成799萬，月付約3.07萬（2.29%）／約2.86萬（新青安1.775%）</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>以總價1,438萬計：貸80成1,150萬，月付約4.42萬（2.29%）／約4.12萬（新青安1.775%）
+          <t>以總價1,438萬計：貸8成1,150萬，月付約4.42萬（2.29%）／約4.12萬（新青安1.775%）
 !超出新青安1,000萬額度部分需按一般房貸利率計息</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>以總價896萬計：貸80成717萬，月付約2.76萬（2.29%）／約2.57萬（新青安1.775%）</t>
+          <t>以總價896萬計：貸8成717萬，月付約2.76萬（2.29%）／約2.57萬（新青安1.775%）</t>
         </is>
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>以總價1,165萬計：貸80成932萬，月付約3.58萬（2.29%）／約3.34萬（新青安1.775%）
+          <t>以總價1,165萬計：貸8成932萬，月付約3.58萬（2.29%）／約3.34萬（新青安1.775%）
 !小坪數套房銀行常只給6~7成，務必先詢價</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>以總價1,300萬計：貸70成910萬，月付約3.50萬（2.29%）／約3.26萬（新青安1.775%）（本案付款結構為貸款70%）
-以總價1,630萬計：貸70成1,141萬，月付約4.38萬（2.29%）／約4.09萬（新青安1.775%）</t>
+          <t>以總價1,300萬計：貸7成910萬，月付約3.50萬（2.29%）／約3.26萬（新青安1.775%）（本案付款結構為貸款70%）
+以總價1,630萬計：貸7成1,141萬，月付約4.38萬（2.29%）／約4.09萬（新青安1.775%）</t>
         </is>
       </c>
       <c r="I7" s="8" t="inlineStr">
         <is>
-          <t>以總價988萬計：貸80成790萬，月付約3.04萬（2.29%）／約2.83萬（新青安1.775%）</t>
+          <t>以總價988萬計：貸8成790萬，月付約3.04萬（2.29%）／約2.83萬（新青安1.775%）</t>
         </is>
       </c>
     </row>
